--- a/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/gemini_gemini-3-pro-preview-thinking_judge_medium__vs__qwen_qwen3.8-max_judge_medium.xlsx
+++ b/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/gemini_gemini-3-pro-preview-thinking_judge_medium__vs__qwen_qwen3.8-max_judge_medium.xlsx
@@ -2056,33 +2056,35 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>10031.88850003062</v>
+        <v>9541.966999997385</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03641698276624084</v>
+        <v>1420.720750000328</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2121,33 +2123,35 @@
       <c r="H3" t="b">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>2333.422792027704</v>
+        <v>9185.343625023961</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01554196933284402</v>
+        <v>1734.333458996844</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2186,33 +2190,35 @@
       <c r="H4" t="b">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>6766.277417016681</v>
+        <v>9762.359334039502</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01883297227323055</v>
+        <v>1496.938167023472</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2251,33 +2257,35 @@
       <c r="H5" t="b">
         <v>1</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>17457.68866699655</v>
+        <v>10841.31862502545</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03299996023997664</v>
+        <v>1591.271249984857</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2316,33 +2324,35 @@
       <c r="H6" t="b">
         <v>1</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>38087.34974998515</v>
+        <v>10737.70741699263</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1283750170841813</v>
+        <v>1368.95408295095</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2381,33 +2391,35 @@
       <c r="H7" t="b">
         <v>1</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>14002.24899995374</v>
+        <v>11370.38737500552</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01929199788719416</v>
+        <v>1093.327334034257</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2446,33 +2458,35 @@
       <c r="H8" t="b">
         <v>1</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>5626.037334033754</v>
+        <v>8522.680708032567</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03316602669656277</v>
+        <v>2013.580999977421</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2511,33 +2525,35 @@
       <c r="H9" t="b">
         <v>1</v>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.004542001988738775</v>
+        <v>17506.98674999876</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05108298500999808</v>
+        <v>1646.162499964703</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2576,33 +2592,35 @@
       <c r="H10" t="b">
         <v>1</v>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>0.005167035851627588</v>
+        <v>10788.03033399163</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02020801184698939</v>
+        <v>1285.620582988486</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2641,33 +2659,35 @@
       <c r="H11" t="b">
         <v>1</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>11864.07433304703</v>
+        <v>11086.86875004787</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02916599623858929</v>
+        <v>1135.430124995764</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2706,33 +2726,35 @@
       <c r="H12" t="b">
         <v>1</v>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>9585.57945798384</v>
+        <v>8108.444708981551</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03445800393819809</v>
+        <v>1076.20416599093</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2771,33 +2793,35 @@
       <c r="H13" t="b">
         <v>1</v>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>219.6132499957457</v>
+        <v>15112.66920802882</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02870900789275765</v>
+        <v>1438.793583016377</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2836,33 +2860,35 @@
       <c r="H14" t="b">
         <v>1</v>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>16147.01179199619</v>
+        <v>10812.21633398673</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01224997686222196</v>
+        <v>1983.944333042018</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2901,33 +2927,35 @@
       <c r="H15" t="b">
         <v>1</v>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>276.8410409917124</v>
+        <v>9019.77008295944</v>
       </c>
       <c r="M15" t="n">
-        <v>0.03641698276624084</v>
+        <v>1515.600790968165</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2966,33 +2994,35 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>12436.26995902741</v>
+        <v>11311.3662499818</v>
       </c>
       <c r="M16" t="n">
-        <v>0.03104202914983034</v>
+        <v>1587.420042022131</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3031,33 +3061,35 @@
       <c r="H17" t="b">
         <v>1</v>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>117768.7666249694</v>
+        <v>10100.50012503052</v>
       </c>
       <c r="M17" t="n">
-        <v>0.08037500083446503</v>
+        <v>1098.399166017771</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3096,33 +3128,35 @@
       <c r="H18" t="b">
         <v>1</v>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>9543.376583023928</v>
+        <v>11469.74800003227</v>
       </c>
       <c r="M18" t="n">
-        <v>0.04537496715784073</v>
+        <v>1980.772792012431</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
